--- a/InputData/fuels/MPIiFP/Max Perc Inc in Fuel Production.xlsx
+++ b/InputData/fuels/MPIiFP/Max Perc Inc in Fuel Production.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\fuels\MPIiFP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0B8ACB-4BBF-4525-8677-0DFE86381780}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,11 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>none needed for U.S.</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -103,6 +105,12 @@
     <t>may increase in response to policies.</t>
   </si>
   <si>
+    <t>For the U.S., we do not wish to impose a cap,</t>
+  </si>
+  <si>
+    <t>so we pick an arbitrarily high percentage.</t>
+  </si>
+  <si>
     <t>MPIiFP Maximum Percentage Increase in Fuel Production</t>
   </si>
   <si>
@@ -113,36 +121,12 @@
   </si>
   <si>
     <t>technically recoverable oil deposits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Indian govt. has recently introduced major reforms in </t>
-  </si>
-  <si>
-    <t>exploration and licensing policies to meet domestic consumption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">needs for oil and gas from existing fields and reduce oil import </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dependence (above source). Hence, we do not consider it </t>
-  </si>
-  <si>
-    <t>realistic to impose a cap, and pick an arbitrarily high percentage.</t>
-  </si>
-  <si>
-    <t>Ministry of Petroleum and Natural Gas/ Press Information Bureau</t>
-  </si>
-  <si>
-    <t>Initiatives taken for Increasing Domestic Production of Oil and Gas</t>
-  </si>
-  <si>
-    <t>https://pib.gov.in/newsite/PrintRelease.aspx?relid=190667</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -160,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,12 +154,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -192,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -207,10 +185,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,89 +465,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="59.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="10">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>36</v>
+      <c r="B3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -595,7 +536,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
@@ -702,7 +643,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="6">
         <v>0</v>
@@ -809,7 +750,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -916,7 +857,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -1023,7 +964,7 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1130,7 +1071,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="6">
         <v>0</v>
@@ -1237,7 +1178,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -1344,7 +1285,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6">
         <v>0</v>
@@ -1451,7 +1392,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1558,7 +1499,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1665,7 +1606,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1772,7 +1713,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -1879,7 +1820,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -1986,7 +1927,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2093,7 +2034,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -2200,7 +2141,7 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="6">
         <v>0</v>
@@ -2307,7 +2248,7 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2414,7 +2355,7 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2521,7 +2462,7 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2628,7 +2569,7 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2735,7 +2676,7 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -2842,7 +2783,7 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>999</v>

--- a/InputData/fuels/MPIiFP/Max Perc Inc in Fuel Production.xlsx
+++ b/InputData/fuels/MPIiFP/Max Perc Inc in Fuel Production.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/fuels/MPIiFP/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BC8DFC788DCFEA06A837B21D23CC6D1280E8D25E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A21761E-808B-4240-A72E-475BA4FCE016}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
+    <workbookView xWindow="28695" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,15 +28,33 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
+    <t>MPIiFP Maximum Percentage Increase in Fuel Production</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>none needed for U.S.</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>This variable allows you to specify a cap on how much fuel production</t>
+  </si>
+  <si>
+    <t>may increase in response to policies.</t>
+  </si>
+  <si>
+    <t>This can reflect physical constraints on production, such as limited</t>
+  </si>
+  <si>
+    <t>technically recoverable oil deposits.</t>
+  </si>
+  <si>
+    <t>so we pick an arbitrarily high percentage.</t>
+  </si>
+  <si>
+    <t>Max Percentage Increase (dimensionless)</t>
+  </si>
+  <si>
     <t>electricity (not used in this variable)</t>
   </si>
   <si>
@@ -99,34 +118,16 @@
     <t>hydrogen</t>
   </si>
   <si>
-    <t>Max Percentage Increase (dimensionless)</t>
-  </si>
-  <si>
-    <t>may increase in response to policies.</t>
-  </si>
-  <si>
-    <t>For the U.S., we do not wish to impose a cap,</t>
-  </si>
-  <si>
-    <t>so we pick an arbitrarily high percentage.</t>
-  </si>
-  <si>
-    <t>MPIiFP Maximum Percentage Increase in Fuel Production</t>
-  </si>
-  <si>
-    <t>This variable allows you to specify a cap on how much fuel production</t>
-  </si>
-  <si>
-    <t>This can reflect physical constraints on production, such as limited</t>
-  </si>
-  <si>
-    <t>technically recoverable oil deposits.</t>
+    <t>none needed</t>
+  </si>
+  <si>
+    <t>For the India, we do not wish to impose a cap,</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -170,20 +171,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,56 +463,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -524,233 +522,233 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="36.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1">
         <v>2018</v>
       </c>
       <c r="D1" s="3">
         <v>2019</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>2020</v>
       </c>
       <c r="F1" s="3">
         <v>2021</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1">
         <v>2022</v>
       </c>
       <c r="H1" s="3">
         <v>2023</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1">
         <v>2024</v>
       </c>
       <c r="J1" s="3">
         <v>2025</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1">
         <v>2026</v>
       </c>
       <c r="L1" s="3">
         <v>2027</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1">
         <v>2028</v>
       </c>
       <c r="N1" s="3">
         <v>2029</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1">
         <v>2030</v>
       </c>
       <c r="P1" s="3">
         <v>2031</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1">
         <v>2032</v>
       </c>
       <c r="R1" s="3">
         <v>2033</v>
       </c>
-      <c r="S1" s="4">
+      <c r="S1">
         <v>2034</v>
       </c>
       <c r="T1" s="3">
         <v>2035</v>
       </c>
-      <c r="U1" s="4">
+      <c r="U1">
         <v>2036</v>
       </c>
       <c r="V1" s="3">
         <v>2037</v>
       </c>
-      <c r="W1" s="4">
+      <c r="W1">
         <v>2038</v>
       </c>
       <c r="X1" s="3">
         <v>2039</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Y1">
         <v>2040</v>
       </c>
       <c r="Z1" s="3">
         <v>2041</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AA1">
         <v>2042</v>
       </c>
       <c r="AB1" s="3">
         <v>2043</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AC1">
         <v>2044</v>
       </c>
       <c r="AD1" s="3">
         <v>2045</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AE1">
         <v>2046</v>
       </c>
       <c r="AF1" s="3">
         <v>2047</v>
       </c>
-      <c r="AG1" s="4">
+      <c r="AG1">
         <v>2048</v>
       </c>
       <c r="AH1" s="3">
         <v>2049</v>
       </c>
-      <c r="AI1" s="4">
+      <c r="AI1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="6">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -855,9 +853,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -962,9 +960,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1069,330 +1067,330 @@
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="6">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1497,9 +1495,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>17</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1604,9 +1602,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>18</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1711,9 +1709,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>19</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -1818,9 +1816,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -1925,9 +1923,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>21</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2032,223 +2030,223 @@
         <v>999</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="6">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>0</v>
-      </c>
-      <c r="W16" s="6">
-        <v>0</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="6">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>24</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2353,9 +2351,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>19</v>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>25</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2460,9 +2458,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2567,9 +2565,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>27</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2674,9 +2672,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>28</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -2781,9 +2779,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
       </c>
       <c r="B22">
         <v>999</v>
@@ -2891,4 +2889,184 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F19276E0-E66D-4B75-BF11-D02B461F5C72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6486F85C-272A-443A-B051-D2D28BF743F0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{502BE043-4747-4A79-B368-8F29E08C8DCD}"/>
 </file>